--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.66956269687563</v>
+        <v>12.13380393824229</v>
       </c>
       <c r="D2" t="n">
-        <v>75.11278347901639</v>
+        <v>12.20582731534016</v>
       </c>
       <c r="E2" t="n">
-        <v>17.59426209934285</v>
+        <v>2.859067591143212</v>
       </c>
       <c r="F2" t="n">
-        <v>24.37194758341544</v>
+        <v>3.96044148230501</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.82217799990018</v>
+        <v>6.308603924983779</v>
       </c>
       <c r="D3" t="n">
-        <v>38.29178170628452</v>
+        <v>6.222414527271235</v>
       </c>
       <c r="E3" t="n">
-        <v>17.59426209934285</v>
+        <v>2.859067591143212</v>
       </c>
       <c r="F3" t="n">
-        <v>24.37194758341544</v>
+        <v>3.96044148230501</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>65.03174392270611</v>
+        <v>10.56765838743974</v>
       </c>
       <c r="D4" t="n">
-        <v>64.4190395973942</v>
+        <v>10.46809393457656</v>
       </c>
       <c r="E4" t="n">
-        <v>17.59426209934285</v>
+        <v>2.859067591143212</v>
       </c>
       <c r="F4" t="n">
-        <v>24.37194758341544</v>
+        <v>3.96044148230501</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.02546911377991</v>
+        <v>2.929138730989235</v>
       </c>
       <c r="D5" t="n">
-        <v>9.604686356149273</v>
+        <v>1.560761532874257</v>
       </c>
       <c r="E5" t="n">
-        <v>17.59426209934285</v>
+        <v>2.859067591143212</v>
       </c>
       <c r="F5" t="n">
-        <v>24.37194758341544</v>
+        <v>3.96044148230501</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>51.22634377754819</v>
+        <v>8.324280863851582</v>
       </c>
       <c r="D6" t="n">
-        <v>21.50290750678236</v>
+        <v>3.494222469852133</v>
       </c>
       <c r="E6" t="n">
-        <v>17.59426209934285</v>
+        <v>2.859067591143212</v>
       </c>
       <c r="F6" t="n">
-        <v>24.37194758341544</v>
+        <v>3.96044148230501</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>44.51549051661313</v>
+        <v>7.233767208949635</v>
       </c>
       <c r="D7" t="n">
-        <v>13.5728339133642</v>
+        <v>2.205585510921683</v>
       </c>
       <c r="E7" t="n">
-        <v>17.59426209934285</v>
+        <v>2.859067591143212</v>
       </c>
       <c r="F7" t="n">
-        <v>24.37194758341544</v>
+        <v>3.96044148230501</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>62.52099337462699</v>
+        <v>10.15966142337689</v>
       </c>
       <c r="D8" t="n">
-        <v>59.0196414231886</v>
+        <v>9.590691731268148</v>
       </c>
       <c r="E8" t="n">
-        <v>17.59426209934285</v>
+        <v>2.859067591143212</v>
       </c>
       <c r="F8" t="n">
-        <v>24.37194758341544</v>
+        <v>3.96044148230501</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
